--- a/grupos/6APV - Estadisticos 20222.xlsx
+++ b/grupos/6APV - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="80">
   <si>
     <t>Materia</t>
   </si>
@@ -174,148 +173,100 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>BALTAZARES</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>DE LUNA</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>OJEDA</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>TINOCO</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
     <t>CARRASCO</t>
   </si>
   <si>
     <t>CORDOVA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>REYES</t>
+    <t>ELIAS ALONSO</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL ONAM</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
+    <t>IRVING JAIR</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
   </si>
   <si>
     <t>IVETTE</t>
   </si>
   <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>IAN URIEL</t>
-  </si>
-  <si>
-    <t>JESUS HUMBERTO</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
     <t>KARLA RENATA</t>
   </si>
   <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
     <t>EUDY</t>
   </si>
   <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
     <t>KAREN YAZMIN</t>
   </si>
   <si>
-    <t>IRVING JAIR</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
     <t>DANTE GAMALIEL</t>
-  </si>
-  <si>
-    <t>AXEL YAEL</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -368,11 +319,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -813,22 +765,22 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -849,19 +801,19 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>6</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -890,22 +842,22 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -967,22 +919,22 @@
         <v>4</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1006,10 +958,10 @@
         <v>7</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>5</v>
@@ -1044,22 +996,22 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1092,10 +1044,10 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1121,22 +1073,22 @@
         <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1157,7 +1109,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1169,7 +1121,7 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>6</v>
@@ -1198,22 +1150,22 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1237,16 +1189,16 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>10</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>10</v>
@@ -1275,22 +1227,22 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1311,13 +1263,13 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>9</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>6</v>
@@ -1352,22 +1304,22 @@
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1394,13 +1346,13 @@
         <v>9</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>6</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1429,22 +1381,22 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1465,13 +1417,13 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>8</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1506,22 +1458,22 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1542,19 +1494,19 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>9</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>5</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1583,22 +1535,22 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1625,13 +1577,13 @@
         <v>9</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>8</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1660,22 +1612,22 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1699,16 +1651,16 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>8</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -1737,22 +1689,22 @@
         <v>4</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1776,10 +1728,10 @@
         <v>8</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -1814,22 +1766,22 @@
         <v>4</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1850,13 +1802,13 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>6</v>
@@ -1891,22 +1843,22 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1927,19 +1879,19 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>7</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -1968,22 +1920,22 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2004,22 +1956,22 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>7</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2045,22 +1997,22 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2081,19 +2033,19 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>8</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2232,22 +2184,22 @@
         <v>92</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -2291,22 +2243,22 @@
         <v>92</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -2350,22 +2302,22 @@
         <v>76</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -2409,22 +2361,22 @@
         <v>92</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -2468,22 +2420,22 @@
         <v>92</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -2527,22 +2479,22 @@
         <v>92</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -2586,22 +2538,22 @@
         <v>92</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -2645,22 +2597,22 @@
         <v>92</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -2704,22 +2656,22 @@
         <v>92</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -2763,22 +2715,22 @@
         <v>92</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2822,22 +2774,22 @@
         <v>92</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2881,22 +2833,22 @@
         <v>92</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2940,22 +2892,22 @@
         <v>76</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2999,22 +2951,22 @@
         <v>76</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3058,22 +3010,22 @@
         <v>92</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -3117,22 +3069,22 @@
         <v>92</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -3176,22 +3128,22 @@
         <v>92</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -3228,6 +3180,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -3273,24 +3227,24 @@
         <v>17</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>10</v>
-      </c>
-      <c r="F2">
-        <v>41.18</v>
-      </c>
-      <c r="G2">
-        <v>58.82</v>
+        <v>11</v>
+      </c>
+      <c r="F2" s="2">
+        <v>35.3</v>
+      </c>
+      <c r="G2" s="2">
+        <v>64.7</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3305,24 +3259,24 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>58.82</v>
-      </c>
-      <c r="G3">
-        <v>41.18</v>
+        <v>5</v>
+      </c>
+      <c r="F3" s="2">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="G3" s="2">
+        <v>29.4</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3342,11 +3296,11 @@
       <c r="E4">
         <v>2</v>
       </c>
-      <c r="F4">
-        <v>88.23999999999999</v>
-      </c>
-      <c r="G4">
-        <v>11.76</v>
+      <c r="F4" s="2">
+        <v>88.2</v>
+      </c>
+      <c r="G4" s="2">
+        <v>11.8</v>
       </c>
       <c r="H4">
         <v>7.1</v>
@@ -3354,7 +3308,7 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3374,19 +3328,19 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="G5">
+      <c r="F5" s="2">
+        <v>100</v>
+      </c>
+      <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3406,19 +3360,19 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>100</v>
-      </c>
-      <c r="G6">
+      <c r="F6" s="2">
+        <v>100</v>
+      </c>
+      <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3438,19 +3392,19 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>100</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="2">
+        <v>100</v>
+      </c>
+      <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3495,327 +3449,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>20330051920260</v>
-      </c>
-      <c r="B2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>19330051920314</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>20330051920262</v>
-      </c>
-      <c r="B4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>20330051920268</v>
-      </c>
-      <c r="B5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>20330051920269</v>
-      </c>
-      <c r="B6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>20330051920270</v>
-      </c>
-      <c r="B7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>20330051920271</v>
-      </c>
-      <c r="B8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>20330051920272</v>
-      </c>
-      <c r="B9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>19220030050208</v>
-      </c>
-      <c r="B10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>20330051920273</v>
-      </c>
-      <c r="B11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>20330051920274</v>
-      </c>
-      <c r="B12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>20330051920276</v>
-      </c>
-      <c r="B13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" t="s">
-        <v>91</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>19330051920238</v>
-      </c>
-      <c r="B14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" t="s">
-        <v>92</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>20330051920278</v>
-      </c>
-      <c r="B15" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" t="s">
-        <v>93</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>19330051920241</v>
-      </c>
-      <c r="B16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>20330051920279</v>
-      </c>
-      <c r="B17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>20330051920282</v>
-      </c>
-      <c r="B18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" t="s">
-        <v>63</v>
-      </c>
-      <c r="D18" t="s">
-        <v>96</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3847,16 +3481,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920260</v>
+        <v>20330051920270</v>
       </c>
       <c r="B2" t="s">
         <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -3870,16 +3504,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920260</v>
+        <v>20330051920270</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3893,16 +3527,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920270</v>
+        <v>20330051920272</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" t="s">
         <v>71</v>
-      </c>
-      <c r="D4" t="s">
-        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -3916,16 +3550,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920270</v>
+        <v>20330051920272</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" t="s">
         <v>71</v>
-      </c>
-      <c r="D5" t="s">
-        <v>85</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -3939,22 +3573,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920272</v>
+        <v>20330051920273</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3962,16 +3596,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920272</v>
+        <v>20330051920273</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -3988,13 +3622,13 @@
         <v>19330051920238</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -4011,13 +3645,13 @@
         <v>19330051920238</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -4034,13 +3668,13 @@
         <v>20330051920278</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -4057,13 +3691,13 @@
         <v>20330051920278</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -4077,16 +3711,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920271</v>
+        <v>20330051920260</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -4100,16 +3734,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920276</v>
+        <v>20330051920271</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -4123,16 +3757,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920241</v>
+        <v>19220030050208</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -4141,6 +3775,52 @@
         <v>41</v>
       </c>
       <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920276</v>
+      </c>
+      <c r="B15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>19330051920241</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6APV - Estadisticos 20222.xlsx
+++ b/grupos/6APV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="80">
   <si>
     <t>Materia</t>
   </si>
@@ -179,21 +179,21 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
     <t>OJEDA</t>
   </si>
   <si>
@@ -206,24 +206,24 @@
     <t>SANTIAGO</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
@@ -236,22 +236,22 @@
     <t>MIGUEL ANGEL ONAM</t>
   </si>
   <si>
+    <t>IRVING JAIR</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>IVETTE</t>
+  </si>
+  <si>
+    <t>KARLA RENATA</t>
+  </si>
+  <si>
+    <t>EUDY</t>
+  </si>
+  <si>
     <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>KARLA RENATA</t>
-  </si>
-  <si>
-    <t>EUDY</t>
   </si>
   <si>
     <t>KAREN YAZMIN</t>
@@ -851,7 +851,7 @@
         <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>7</v>
@@ -928,7 +928,7 @@
         <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>4</v>
@@ -1005,7 +1005,7 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>6</v>
@@ -1082,7 +1082,7 @@
         <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>9</v>
@@ -1118,7 +1118,7 @@
         <v>10</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -1159,7 +1159,7 @@
         <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>8</v>
@@ -1390,7 +1390,7 @@
         <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>6</v>
@@ -1467,7 +1467,7 @@
         <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
         <v>7</v>
@@ -1503,7 +1503,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>6</v>
@@ -1544,7 +1544,7 @@
         <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>8</v>
@@ -1621,7 +1621,7 @@
         <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
         <v>9</v>
@@ -1657,7 +1657,7 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1698,7 +1698,7 @@
         <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>4</v>
@@ -1852,7 +1852,7 @@
         <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>6</v>
@@ -1888,7 +1888,7 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>7</v>
@@ -2006,7 +2006,7 @@
         <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>8</v>
@@ -2042,7 +2042,7 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -2193,7 +2193,7 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>108</v>
@@ -2252,7 +2252,7 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>112</v>
@@ -2311,7 +2311,7 @@
         <v>76</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="L6">
         <v>72</v>
@@ -2370,7 +2370,7 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>116</v>
@@ -2429,7 +2429,7 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
         <v>120</v>
@@ -2488,7 +2488,7 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
         <v>116</v>
@@ -2547,7 +2547,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -2606,7 +2606,7 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>104</v>
@@ -2665,7 +2665,7 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>120</v>
@@ -2724,7 +2724,7 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
         <v>108</v>
@@ -2783,7 +2783,7 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>116</v>
@@ -2842,7 +2842,7 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
         <v>104</v>
@@ -2901,7 +2901,7 @@
         <v>76</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="L16">
         <v>92</v>
@@ -2960,7 +2960,7 @@
         <v>76</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L17">
         <v>108</v>
@@ -3019,7 +3019,7 @@
         <v>88</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
         <v>104</v>
@@ -3078,7 +3078,7 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>116</v>
@@ -3137,7 +3137,7 @@
         <v>76</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>88</v>
@@ -3291,19 +3291,19 @@
         <v>17</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>11.8</v>
+        <v>5.9</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3449,7 +3449,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3573,7 +3573,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920273</v>
+        <v>19330051920238</v>
       </c>
       <c r="B6" t="s">
         <v>53</v>
@@ -3585,10 +3585,10 @@
         <v>72</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3596,7 +3596,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920273</v>
+        <v>19330051920238</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
@@ -3619,7 +3619,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920238</v>
+        <v>20330051920278</v>
       </c>
       <c r="B8" t="s">
         <v>54</v>
@@ -3642,7 +3642,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920238</v>
+        <v>20330051920278</v>
       </c>
       <c r="B9" t="s">
         <v>54</v>
@@ -3665,7 +3665,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920278</v>
+        <v>20330051920260</v>
       </c>
       <c r="B10" t="s">
         <v>55</v>
@@ -3677,10 +3677,10 @@
         <v>74</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -3688,16 +3688,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920278</v>
+        <v>20330051920271</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -3711,16 +3711,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920260</v>
+        <v>19220030050208</v>
       </c>
       <c r="B12" t="s">
         <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -3734,16 +3734,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920271</v>
+        <v>20330051920273</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -3757,16 +3757,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19220030050208</v>
+        <v>20330051920276</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -3780,16 +3780,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920276</v>
+        <v>19330051920241</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -3798,29 +3798,6 @@
         <v>41</v>
       </c>
       <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19330051920241</v>
-      </c>
-      <c r="B16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" t="s">
-        <v>79</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6APV - Estadisticos 20222.xlsx
+++ b/grupos/6APV - Estadisticos 20222.xlsx
@@ -774,7 +774,7 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -1236,7 +1236,7 @@
         <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>6</v>
@@ -1313,7 +1313,7 @@
         <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>7</v>
@@ -1775,7 +1775,7 @@
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>6</v>

--- a/grupos/6APV - Estadisticos 20222.xlsx
+++ b/grupos/6APV - Estadisticos 20222.xlsx
@@ -2175,13 +2175,13 @@
         <v>100</v>
       </c>
       <c r="E4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>100</v>
       </c>
       <c r="G4">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>93.3</v>
@@ -2196,28 +2196,28 @@
         <v>100</v>
       </c>
       <c r="L4">
-        <v>108</v>
+        <v>94.5</v>
       </c>
       <c r="M4">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>94.5</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2234,49 +2234,49 @@
         <v>92</v>
       </c>
       <c r="E5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>100</v>
       </c>
       <c r="G5">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>86.7</v>
+        <v>85</v>
       </c>
       <c r="I5">
         <v>100</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K5">
         <v>100</v>
       </c>
       <c r="L5">
-        <v>112</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M5">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2293,49 +2293,49 @@
         <v>88</v>
       </c>
       <c r="E6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F6">
         <v>80</v>
       </c>
       <c r="G6">
-        <v>76</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H6">
-        <v>93.3</v>
+        <v>70</v>
       </c>
       <c r="I6">
         <v>100</v>
       </c>
       <c r="J6">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K6">
-        <v>88</v>
+        <v>94.5</v>
       </c>
       <c r="L6">
-        <v>72</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="M6">
-        <v>84</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>94.5</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2352,16 +2352,16 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>100</v>
       </c>
       <c r="G7">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I7">
         <v>100</v>
@@ -2373,28 +2373,28 @@
         <v>100</v>
       </c>
       <c r="L7">
-        <v>116</v>
+        <v>98.2</v>
       </c>
       <c r="M7">
-        <v>96</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2411,16 +2411,16 @@
         <v>100</v>
       </c>
       <c r="E8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>100</v>
       </c>
       <c r="G8">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="I8">
         <v>100</v>
@@ -2432,28 +2432,28 @@
         <v>100</v>
       </c>
       <c r="L8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M8">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2470,49 +2470,49 @@
         <v>92</v>
       </c>
       <c r="E9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <v>100</v>
       </c>
       <c r="G9">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H9">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I9">
         <v>100</v>
       </c>
       <c r="J9">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>116</v>
+        <v>98.2</v>
       </c>
       <c r="M9">
-        <v>84</v>
+        <v>89.8</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -2529,49 +2529,49 @@
         <v>92</v>
       </c>
       <c r="E10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F10">
         <v>96</v>
       </c>
       <c r="G10">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H10">
-        <v>86.7</v>
+        <v>81.7</v>
       </c>
       <c r="I10">
         <v>100</v>
       </c>
       <c r="J10">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K10">
         <v>100</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="M10">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="N10">
+        <v>81.7</v>
+      </c>
+      <c r="O10">
+        <v>100</v>
+      </c>
+      <c r="P10">
         <v>96</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -2588,49 +2588,49 @@
         <v>96</v>
       </c>
       <c r="E11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F11">
         <v>84</v>
       </c>
       <c r="G11">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H11">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="I11">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J11">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K11">
         <v>100</v>
       </c>
       <c r="L11">
-        <v>104</v>
+        <v>85.5</v>
       </c>
       <c r="M11">
-        <v>84</v>
+        <v>89.8</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>85.5</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -2647,49 +2647,49 @@
         <v>96</v>
       </c>
       <c r="E12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>100</v>
       </c>
       <c r="G12">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H12">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="I12">
         <v>100</v>
       </c>
       <c r="J12">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K12">
         <v>100</v>
       </c>
       <c r="L12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M12">
-        <v>84</v>
+        <v>89.8</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -2706,13 +2706,13 @@
         <v>88</v>
       </c>
       <c r="E13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F13">
         <v>100</v>
       </c>
       <c r="G13">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H13">
         <v>80</v>
@@ -2721,34 +2721,34 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="K13">
         <v>100</v>
       </c>
       <c r="L13">
-        <v>108</v>
+        <v>94.5</v>
       </c>
       <c r="M13">
-        <v>84</v>
+        <v>89.8</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>94.5</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -2765,16 +2765,16 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>84</v>
       </c>
       <c r="G14">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H14">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I14">
         <v>100</v>
@@ -2786,28 +2786,28 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>116</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M14">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -2824,49 +2824,49 @@
         <v>92</v>
       </c>
       <c r="E15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F15">
         <v>100</v>
       </c>
       <c r="G15">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H15">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="I15">
         <v>100</v>
       </c>
       <c r="J15">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K15">
         <v>100</v>
       </c>
       <c r="L15">
-        <v>104</v>
+        <v>92.7</v>
       </c>
       <c r="M15">
-        <v>84</v>
+        <v>89.8</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -2883,49 +2883,49 @@
         <v>88</v>
       </c>
       <c r="E16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>96</v>
       </c>
       <c r="G16">
-        <v>76</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H16">
-        <v>100</v>
+        <v>73.3</v>
       </c>
       <c r="I16">
         <v>100</v>
       </c>
       <c r="J16">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K16">
-        <v>88</v>
+        <v>94.5</v>
       </c>
       <c r="L16">
-        <v>92</v>
+        <v>85.5</v>
       </c>
       <c r="M16">
-        <v>84</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>94.5</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>85.5</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -2942,49 +2942,49 @@
         <v>92</v>
       </c>
       <c r="E17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>92</v>
       </c>
       <c r="G17">
-        <v>76</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H17">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="I17">
         <v>100</v>
       </c>
       <c r="J17">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="K17">
-        <v>96</v>
+        <v>98.2</v>
       </c>
       <c r="L17">
-        <v>108</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M17">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="N17">
+        <v>95</v>
+      </c>
+      <c r="O17">
+        <v>100</v>
+      </c>
+      <c r="P17">
         <v>84</v>
       </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
       <c r="Q17">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3001,49 +3001,49 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>100</v>
       </c>
       <c r="G18">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H18">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="I18">
         <v>100</v>
       </c>
       <c r="J18">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K18">
         <v>100</v>
       </c>
       <c r="L18">
-        <v>104</v>
+        <v>92.7</v>
       </c>
       <c r="M18">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3060,13 +3060,13 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F19">
         <v>100</v>
       </c>
       <c r="G19">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H19">
         <v>96.7</v>
@@ -3081,28 +3081,28 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>116</v>
+        <v>98.2</v>
       </c>
       <c r="M19">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3119,49 +3119,49 @@
         <v>100</v>
       </c>
       <c r="E20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>92</v>
       </c>
       <c r="G20">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H20">
-        <v>80</v>
+        <v>88.3</v>
       </c>
       <c r="I20">
         <v>100</v>
       </c>
       <c r="J20">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="K20">
         <v>100</v>
       </c>
       <c r="L20">
+        <v>81.8</v>
+      </c>
+      <c r="M20">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="N20">
+        <v>88.3</v>
+      </c>
+      <c r="O20">
+        <v>100</v>
+      </c>
+      <c r="P20">
         <v>88</v>
       </c>
-      <c r="M20">
-        <v>92</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
       <c r="Q20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6APV - Estadisticos 20222.xlsx
+++ b/grupos/6APV - Estadisticos 20222.xlsx
@@ -2184,7 +2184,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>93.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I4">
         <v>100</v>
@@ -2202,7 +2202,7 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>93.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -2243,7 +2243,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>85</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I5">
         <v>100</v>
@@ -2261,7 +2261,7 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>85</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -2302,7 +2302,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="H6">
-        <v>70</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I6">
         <v>100</v>
@@ -2320,7 +2320,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="N6">
-        <v>70</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -2361,7 +2361,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="I7">
         <v>100</v>
@@ -2379,7 +2379,7 @@
         <v>95.90000000000001</v>
       </c>
       <c r="N7">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -2420,7 +2420,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>85</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I8">
         <v>100</v>
@@ -2438,7 +2438,7 @@
         <v>98</v>
       </c>
       <c r="N8">
-        <v>85</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -2479,7 +2479,7 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>85</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I9">
         <v>100</v>
@@ -2497,7 +2497,7 @@
         <v>89.8</v>
       </c>
       <c r="N9">
-        <v>85</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -2538,7 +2538,7 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>81.7</v>
+        <v>84.5</v>
       </c>
       <c r="I10">
         <v>100</v>
@@ -2556,7 +2556,7 @@
         <v>95.90000000000001</v>
       </c>
       <c r="N10">
-        <v>81.7</v>
+        <v>84.5</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -2597,7 +2597,7 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>86.7</v>
+        <v>89.7</v>
       </c>
       <c r="I11">
         <v>98.3</v>
@@ -2615,7 +2615,7 @@
         <v>89.8</v>
       </c>
       <c r="N11">
-        <v>86.7</v>
+        <v>89.7</v>
       </c>
       <c r="O11">
         <v>98.3</v>
@@ -2656,7 +2656,7 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>95</v>
+        <v>98.3</v>
       </c>
       <c r="I12">
         <v>100</v>
@@ -2674,7 +2674,7 @@
         <v>89.8</v>
       </c>
       <c r="N12">
-        <v>95</v>
+        <v>98.3</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -2715,7 +2715,7 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>80</v>
+        <v>82.8</v>
       </c>
       <c r="I13">
         <v>100</v>
@@ -2733,7 +2733,7 @@
         <v>89.8</v>
       </c>
       <c r="N13">
-        <v>80</v>
+        <v>82.8</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -2774,7 +2774,7 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="I14">
         <v>100</v>
@@ -2792,7 +2792,7 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -2833,7 +2833,7 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>93.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I15">
         <v>100</v>
@@ -2851,7 +2851,7 @@
         <v>89.8</v>
       </c>
       <c r="N15">
-        <v>93.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O15">
         <v>100</v>
@@ -2892,7 +2892,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="H16">
-        <v>73.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I16">
         <v>100</v>
@@ -2910,7 +2910,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="N16">
-        <v>73.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -2951,7 +2951,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="H17">
-        <v>95</v>
+        <v>98.3</v>
       </c>
       <c r="I17">
         <v>100</v>
@@ -2969,7 +2969,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="N17">
-        <v>95</v>
+        <v>98.3</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -3010,7 +3010,7 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>95</v>
+        <v>98.3</v>
       </c>
       <c r="I18">
         <v>100</v>
@@ -3028,7 +3028,7 @@
         <v>98</v>
       </c>
       <c r="N18">
-        <v>95</v>
+        <v>98.3</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -3069,7 +3069,7 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="I19">
         <v>100</v>
@@ -3087,7 +3087,7 @@
         <v>98</v>
       </c>
       <c r="N19">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -3128,7 +3128,7 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>88.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I20">
         <v>100</v>
@@ -3146,7 +3146,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="N20">
-        <v>88.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="O20">
         <v>100</v>

--- a/grupos/6APV - Estadisticos 20222.xlsx
+++ b/grupos/6APV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="57">
   <si>
     <t>Materia</t>
   </si>
@@ -152,12 +152,12 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
     <t>Santiago Hernández Mariana</t>
   </si>
   <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -173,91 +173,22 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>ORTIZ</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
     <t>IRVING JAIR</t>
   </si>
   <si>
     <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>KARLA RENATA</t>
-  </si>
-  <si>
-    <t>EUDY</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>KAREN YAZMIN</t>
-  </si>
-  <si>
-    <t>DANTE GAMALIEL</t>
   </si>
 </sst>
 </file>
@@ -783,22 +714,22 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
         <v>8</v>
@@ -813,10 +744,10 @@
         <v>6</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -860,22 +791,22 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>8</v>
@@ -937,25 +868,25 @@
         <v>4</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U6">
         <v>9</v>
@@ -1014,22 +945,22 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>7</v>
@@ -1047,7 +978,7 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1091,22 +1022,22 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>7</v>
@@ -1168,22 +1099,22 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1245,25 +1176,25 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -1272,13 +1203,13 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1322,22 +1253,22 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>8</v>
@@ -1355,7 +1286,7 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1399,25 +1330,25 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>8</v>
@@ -1429,10 +1360,10 @@
         <v>6</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1476,25 +1407,25 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>9</v>
@@ -1506,10 +1437,10 @@
         <v>6</v>
       </c>
       <c r="X13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1553,22 +1484,22 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>8</v>
@@ -1580,13 +1511,13 @@
         <v>9</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1630,25 +1561,25 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>9</v>
@@ -1663,7 +1594,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1707,22 +1638,22 @@
         <v>4</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>8</v>
@@ -1734,7 +1665,7 @@
         <v>7</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>5</v>
@@ -1784,22 +1715,22 @@
         <v>4</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -1814,7 +1745,7 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -1861,28 +1792,28 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>8</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -1891,10 +1822,10 @@
         <v>8</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1938,22 +1869,22 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -1965,13 +1896,13 @@
         <v>9</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2015,22 +1946,22 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -2202,7 +2133,7 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>96.59999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -2214,7 +2145,7 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>94.5</v>
+        <v>96.2</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -2261,7 +2192,7 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>87.90000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -2273,7 +2204,7 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>96.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -2320,7 +2251,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="N6">
-        <v>72.40000000000001</v>
+        <v>63</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -2329,13 +2260,13 @@
         <v>82</v>
       </c>
       <c r="Q6">
-        <v>94.5</v>
+        <v>65</v>
       </c>
       <c r="R6">
-        <v>69.09999999999999</v>
+        <v>48.1</v>
       </c>
       <c r="S6">
-        <v>81.59999999999999</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2379,7 +2310,7 @@
         <v>95.90000000000001</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>93.5</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -2391,10 +2322,10 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>98.2</v>
+        <v>98.7</v>
       </c>
       <c r="S7">
-        <v>95.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2438,7 +2369,7 @@
         <v>98</v>
       </c>
       <c r="N8">
-        <v>87.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -2453,7 +2384,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2497,7 +2428,7 @@
         <v>89.8</v>
       </c>
       <c r="N9">
-        <v>87.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -2509,10 +2440,10 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>98.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="S9">
-        <v>89.8</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -2556,7 +2487,7 @@
         <v>95.90000000000001</v>
       </c>
       <c r="N10">
-        <v>84.5</v>
+        <v>87</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -2568,10 +2499,10 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>89.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="S10">
-        <v>95.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -2615,10 +2546,10 @@
         <v>89.8</v>
       </c>
       <c r="N11">
-        <v>89.7</v>
+        <v>83.7</v>
       </c>
       <c r="O11">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P11">
         <v>98</v>
@@ -2627,10 +2558,10 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>85.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S11">
-        <v>89.8</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -2674,7 +2605,7 @@
         <v>89.8</v>
       </c>
       <c r="N12">
-        <v>98.3</v>
+        <v>95.7</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -2689,7 +2620,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>89.8</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -2733,7 +2664,7 @@
         <v>89.8</v>
       </c>
       <c r="N13">
-        <v>82.8</v>
+        <v>87</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -2745,10 +2676,10 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>94.5</v>
+        <v>93.7</v>
       </c>
       <c r="S13">
-        <v>89.8</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -2792,7 +2723,7 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -2804,7 +2735,7 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>90.90000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -2851,7 +2782,7 @@
         <v>89.8</v>
       </c>
       <c r="N15">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="O15">
         <v>100</v>
@@ -2863,10 +2794,10 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>92.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="S15">
-        <v>89.8</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -2910,7 +2841,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="N16">
-        <v>75.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -2919,13 +2850,13 @@
         <v>82</v>
       </c>
       <c r="Q16">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
       <c r="R16">
-        <v>85.5</v>
+        <v>59.5</v>
       </c>
       <c r="S16">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -2969,7 +2900,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="N17">
-        <v>98.3</v>
+        <v>93.5</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -2978,10 +2909,10 @@
         <v>84</v>
       </c>
       <c r="Q17">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
       <c r="R17">
-        <v>90.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="S17">
         <v>81.59999999999999</v>
@@ -3028,7 +2959,7 @@
         <v>98</v>
       </c>
       <c r="N18">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -3040,10 +2971,10 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>92.7</v>
+        <v>96.2</v>
       </c>
       <c r="S18">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3087,7 +3018,7 @@
         <v>98</v>
       </c>
       <c r="N19">
-        <v>100</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -3099,10 +3030,10 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>98.2</v>
+        <v>93.7</v>
       </c>
       <c r="S19">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3146,7 +3077,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="N20">
-        <v>91.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O20">
         <v>100</v>
@@ -3158,10 +3089,10 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>81.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S20">
-        <v>93.90000000000001</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3227,19 +3158,19 @@
         <v>17</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2">
-        <v>35.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>64.7</v>
+        <v>17.6</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3259,19 +3190,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>70.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="G3" s="2">
-        <v>29.4</v>
+        <v>11.8</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3303,7 +3234,7 @@
         <v>5.9</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3314,7 +3245,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>44</v>
@@ -3323,19 +3254,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3346,7 +3277,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>45</v>
@@ -3367,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3399,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3449,7 +3380,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3481,16 +3412,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920270</v>
+        <v>19330051920238</v>
       </c>
       <c r="B2" t="s">
         <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -3504,16 +3435,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920270</v>
+        <v>19330051920238</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3527,277 +3458,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920272</v>
+        <v>20330051920278</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920272</v>
-      </c>
-      <c r="B5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920238</v>
-      </c>
-      <c r="B6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920238</v>
-      </c>
-      <c r="B7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920278</v>
-      </c>
-      <c r="B8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920278</v>
-      </c>
-      <c r="B9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920260</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920271</v>
-      </c>
-      <c r="B11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19220030050208</v>
-      </c>
-      <c r="B12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920273</v>
-      </c>
-      <c r="B13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920276</v>
-      </c>
-      <c r="B14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19330051920241</v>
-      </c>
-      <c r="B15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6APV - Estadisticos 20222.xlsx
+++ b/grupos/6APV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="54">
   <si>
     <t>Materia</t>
   </si>
@@ -149,15 +149,15 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Santiago Hernández Mariana</t>
+  </si>
+  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
-    <t>Santiago Hernández Mariana</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -173,19 +173,10 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
   </si>
   <si>
     <t>MARCO JOSAFAT</t>
@@ -720,7 +711,7 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
         <v>7</v>
@@ -738,7 +729,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>6</v>
@@ -797,7 +788,7 @@
         <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
         <v>10</v>
@@ -815,7 +806,7 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -874,7 +865,7 @@
         <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
         <v>5</v>
@@ -892,7 +883,7 @@
         <v>9</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>5</v>
@@ -951,7 +942,7 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
         <v>8</v>
@@ -1028,7 +1019,7 @@
         <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -1046,7 +1037,7 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1105,7 +1096,7 @@
         <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>10</v>
@@ -1123,7 +1114,7 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1182,7 +1173,7 @@
         <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
         <v>8</v>
@@ -1200,7 +1191,7 @@
         <v>9</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1259,7 +1250,7 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
         <v>6</v>
@@ -1277,7 +1268,7 @@
         <v>9</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>6</v>
@@ -1336,7 +1327,7 @@
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>7</v>
@@ -1413,7 +1404,7 @@
         <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
         <v>7</v>
@@ -1490,7 +1481,7 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
         <v>10</v>
@@ -1508,7 +1499,7 @@
         <v>9</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1567,7 +1558,7 @@
         <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>8</v>
@@ -1644,7 +1635,7 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -1662,7 +1653,7 @@
         <v>8</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>8</v>
@@ -1721,7 +1712,7 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -1798,7 +1789,7 @@
         <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
         <v>9</v>
@@ -1816,7 +1807,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -1875,7 +1866,7 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -1893,7 +1884,7 @@
         <v>9</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -1952,7 +1943,7 @@
         <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2198,7 +2189,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -2257,7 +2248,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>82</v>
+        <v>54.7</v>
       </c>
       <c r="Q6">
         <v>65</v>
@@ -2434,7 +2425,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -2493,7 +2484,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -2552,7 +2543,7 @@
         <v>98.90000000000001</v>
       </c>
       <c r="P11">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -2611,7 +2602,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>98</v>
+        <v>98.7</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -2670,7 +2661,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -2788,7 +2779,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>96</v>
+        <v>97.3</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -2847,7 +2838,7 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>82</v>
+        <v>54.7</v>
       </c>
       <c r="Q16">
         <v>96.3</v>
@@ -2906,7 +2897,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>84</v>
+        <v>89.3</v>
       </c>
       <c r="Q17">
         <v>98.8</v>
@@ -2965,7 +2956,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -3083,7 +3074,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -3213,7 +3204,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>43</v>
@@ -3222,16 +3213,16 @@
         <v>17</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="G4" s="2">
-        <v>5.9</v>
+        <v>11.8</v>
       </c>
       <c r="H4">
         <v>7.5</v>
@@ -3245,7 +3236,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>44</v>
@@ -3266,7 +3257,7 @@
         <v>5.9</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3277,7 +3268,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>45</v>
@@ -3286,19 +3277,19 @@
         <v>17</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3380,7 +3371,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3412,70 +3403,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920238</v>
+        <v>20330051920278</v>
       </c>
       <c r="B2" t="s">
         <v>51</v>
       </c>
       <c r="C2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" t="s">
         <v>53</v>
       </c>
-      <c r="D2" t="s">
-        <v>55</v>
-      </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920238</v>
-      </c>
-      <c r="B3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920278</v>
-      </c>
-      <c r="B4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4">
         <v>5</v>
       </c>
     </row>
